--- a/estadias.xlsx
+++ b/estadias.xlsx
@@ -490,7 +490,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -499,34 +499,34 @@
         <v>1500</v>
       </c>
       <c r="D2">
-        <v>381.363</v>
+        <v>390.717</v>
       </c>
       <c r="E2">
-        <v>25.4</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>1118.637</v>
+        <v>1109.283</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H2">
-        <v>190.576</v>
+        <v>245.504</v>
       </c>
       <c r="I2">
-        <v>98.09</v>
+        <v>105.308</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>92.697</v>
+        <v>39.905</v>
       </c>
       <c r="L2">
-        <v>24.3</v>
+        <v>10.2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -535,12 +535,12 @@
         <v>0</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="2">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -561,19 +561,19 @@
         <v>126</v>
       </c>
       <c r="H3">
-        <v>435.277</v>
+        <v>438.286</v>
       </c>
       <c r="I3">
-        <v>354.774</v>
+        <v>357.882</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1052.911</v>
+        <v>1046.794</v>
       </c>
       <c r="L3">
-        <v>57.1</v>
+        <v>56.8</v>
       </c>
       <c r="M3">
         <v>10</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -599,48 +599,48 @@
         <v>6000</v>
       </c>
       <c r="D4">
-        <v>2094.677</v>
+        <v>2196.953</v>
       </c>
       <c r="E4">
-        <v>34.9</v>
+        <v>36.6</v>
       </c>
       <c r="F4">
-        <v>3905.323</v>
+        <v>3803.047</v>
       </c>
       <c r="G4">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>833.551</v>
+        <v>1012.833</v>
       </c>
       <c r="J4">
-        <v>83.82299999999999</v>
+        <v>45.468</v>
       </c>
       <c r="K4">
-        <v>1177.303</v>
+        <v>1138.652</v>
       </c>
       <c r="L4">
-        <v>56.2</v>
+        <v>51.8</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
+        <v>34</v>
+      </c>
+      <c r="O4">
         <v>28</v>
       </c>
-      <c r="O4">
-        <v>45</v>
-      </c>
       <c r="P4">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="2">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -649,43 +649,43 @@
         <v>5000</v>
       </c>
       <c r="D5">
-        <v>4695.866</v>
+        <v>4489.192</v>
       </c>
       <c r="E5">
-        <v>93.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="F5">
-        <v>304.134</v>
+        <v>510.808</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>3210.686</v>
+        <v>3051.954</v>
       </c>
       <c r="I5">
-        <v>570.525</v>
+        <v>891.037</v>
       </c>
       <c r="J5">
-        <v>125.022</v>
+        <v>215.315</v>
       </c>
       <c r="K5">
-        <v>789.6329999999998</v>
+        <v>330.8859999999998</v>
       </c>
       <c r="L5">
-        <v>16.8</v>
+        <v>7.4</v>
       </c>
       <c r="M5">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N5">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O5">
         <v>55</v>
       </c>
       <c r="P5">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -693,43 +693,43 @@
         <v>20000</v>
       </c>
       <c r="D6">
-        <v>9014.868</v>
+        <v>8919.824000000001</v>
       </c>
       <c r="E6">
-        <v>45.075</v>
+        <v>44.605</v>
       </c>
       <c r="F6">
-        <v>10985.132</v>
+        <v>11080.176</v>
       </c>
       <c r="G6">
         <v>269</v>
       </c>
       <c r="H6">
-        <v>3836.539</v>
+        <v>3735.744</v>
       </c>
       <c r="I6">
-        <v>1856.94</v>
+        <v>2367.06</v>
       </c>
       <c r="J6">
-        <v>208.845</v>
+        <v>260.783</v>
       </c>
       <c r="K6">
-        <v>3112.544</v>
+        <v>2556.237</v>
       </c>
       <c r="L6">
-        <v>44.295</v>
+        <v>39.455</v>
       </c>
       <c r="M6">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N6">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="P6">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/estadias.xlsx
+++ b/estadias.xlsx
@@ -490,7 +490,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -499,19 +499,19 @@
         <v>1500</v>
       </c>
       <c r="D2">
-        <v>390.717</v>
+        <v>248.592</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>16.6</v>
       </c>
       <c r="F2">
-        <v>1109.283</v>
+        <v>1251.408</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2">
-        <v>245.504</v>
+        <v>103.379</v>
       </c>
       <c r="I2">
         <v>105.308</v>
@@ -523,10 +523,10 @@
         <v>39.905</v>
       </c>
       <c r="L2">
-        <v>10.2</v>
+        <v>16.1</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -540,7 +540,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="2">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -549,48 +549,48 @@
         <v>7500</v>
       </c>
       <c r="D3">
-        <v>1842.962</v>
+        <v>1607.304</v>
       </c>
       <c r="E3">
-        <v>24.6</v>
+        <v>21.4</v>
       </c>
       <c r="F3">
-        <v>5657.038</v>
+        <v>5892.696</v>
       </c>
       <c r="G3">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H3">
-        <v>438.286</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>357.882</v>
       </c>
       <c r="J3">
+        <v>409.589</v>
+      </c>
+      <c r="K3">
+        <v>839.8330000000001</v>
+      </c>
+      <c r="L3">
+        <v>52.3</v>
+      </c>
+      <c r="M3">
         <v>0</v>
-      </c>
-      <c r="K3">
-        <v>1046.794</v>
-      </c>
-      <c r="L3">
-        <v>56.8</v>
-      </c>
-      <c r="M3">
-        <v>10</v>
       </c>
       <c r="N3">
         <v>6</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="P3">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -599,48 +599,48 @@
         <v>6000</v>
       </c>
       <c r="D4">
-        <v>2196.953</v>
+        <v>2679.802</v>
       </c>
       <c r="E4">
-        <v>36.6</v>
+        <v>44.7</v>
       </c>
       <c r="F4">
-        <v>3803.047</v>
+        <v>3320.198</v>
       </c>
       <c r="G4">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>536.554</v>
       </c>
       <c r="I4">
-        <v>1012.833</v>
+        <v>1493.913</v>
       </c>
       <c r="J4">
-        <v>45.468</v>
+        <v>236.94</v>
       </c>
       <c r="K4">
-        <v>1138.652</v>
+        <v>412.395</v>
       </c>
       <c r="L4">
-        <v>51.8</v>
+        <v>15.4</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="P4">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="2">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -649,43 +649,43 @@
         <v>5000</v>
       </c>
       <c r="D5">
-        <v>4489.192</v>
+        <v>4696.62</v>
       </c>
       <c r="E5">
-        <v>89.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F5">
-        <v>510.808</v>
+        <v>303.3800000000001</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>3051.954</v>
+        <v>2384.54</v>
       </c>
       <c r="I5">
-        <v>891.037</v>
+        <v>2040.33</v>
       </c>
       <c r="J5">
-        <v>215.315</v>
+        <v>203.084</v>
       </c>
       <c r="K5">
-        <v>330.8859999999998</v>
+        <v>68.666</v>
       </c>
       <c r="L5">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="M5">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="N5">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="O5">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="P5">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -693,43 +693,43 @@
         <v>20000</v>
       </c>
       <c r="D6">
-        <v>8919.824000000001</v>
+        <v>9232.317999999999</v>
       </c>
       <c r="E6">
-        <v>44.605</v>
+        <v>46.155</v>
       </c>
       <c r="F6">
-        <v>11080.176</v>
+        <v>10767.682</v>
       </c>
       <c r="G6">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="H6">
-        <v>3735.744</v>
+        <v>3024.473</v>
       </c>
       <c r="I6">
-        <v>2367.06</v>
+        <v>3997.433</v>
       </c>
       <c r="J6">
-        <v>260.783</v>
+        <v>849.6130000000001</v>
       </c>
       <c r="K6">
-        <v>2556.237</v>
+        <v>1360.799</v>
       </c>
       <c r="L6">
-        <v>39.455</v>
+        <v>25.815</v>
       </c>
       <c r="M6">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="N6">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="O6">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="P6">
-        <v>75</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/estadias.xlsx
+++ b/estadias.xlsx
@@ -490,7 +490,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -499,22 +499,22 @@
         <v>1500</v>
       </c>
       <c r="D2">
-        <v>248.592</v>
+        <v>145.213</v>
       </c>
       <c r="E2">
-        <v>16.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F2">
-        <v>1251.408</v>
+        <v>1354.787</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2">
-        <v>103.379</v>
+        <v>105.308</v>
       </c>
       <c r="I2">
-        <v>105.308</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -523,13 +523,13 @@
         <v>39.905</v>
       </c>
       <c r="L2">
-        <v>16.1</v>
+        <v>27.5</v>
       </c>
       <c r="M2">
         <v>2</v>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -540,7 +540,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="2">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -549,16 +549,16 @@
         <v>7500</v>
       </c>
       <c r="D3">
-        <v>1607.304</v>
+        <v>1657.648</v>
       </c>
       <c r="E3">
-        <v>21.4</v>
+        <v>22.1</v>
       </c>
       <c r="F3">
-        <v>5892.696</v>
+        <v>5842.352</v>
       </c>
       <c r="G3">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -567,13 +567,13 @@
         <v>357.882</v>
       </c>
       <c r="J3">
-        <v>409.589</v>
+        <v>501.047</v>
       </c>
       <c r="K3">
-        <v>839.8330000000001</v>
+        <v>798.7189999999998</v>
       </c>
       <c r="L3">
-        <v>52.3</v>
+        <v>48.2</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -582,15 +582,15 @@
         <v>6</v>
       </c>
       <c r="O3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="2">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
@@ -599,48 +599,48 @@
         <v>6000</v>
       </c>
       <c r="D4">
-        <v>2679.802</v>
+        <v>2932.136</v>
       </c>
       <c r="E4">
-        <v>44.7</v>
+        <v>48.9</v>
       </c>
       <c r="F4">
-        <v>3320.198</v>
+        <v>3067.864</v>
       </c>
       <c r="G4">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="H4">
-        <v>536.554</v>
+        <v>208.856</v>
       </c>
       <c r="I4">
-        <v>1493.913</v>
+        <v>1551.265</v>
       </c>
       <c r="J4">
-        <v>236.94</v>
+        <v>714.886</v>
       </c>
       <c r="K4">
-        <v>412.395</v>
+        <v>457.1289999999999</v>
       </c>
       <c r="L4">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="M4">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O4">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="P4">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="2">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -649,43 +649,43 @@
         <v>5000</v>
       </c>
       <c r="D5">
-        <v>4696.62</v>
+        <v>4491.187999999999</v>
       </c>
       <c r="E5">
-        <v>93.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="F5">
-        <v>303.3800000000001</v>
+        <v>508.8120000000008</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>2384.54</v>
+        <v>3562.293</v>
       </c>
       <c r="I5">
-        <v>2040.33</v>
+        <v>505.146</v>
       </c>
       <c r="J5">
-        <v>203.084</v>
+        <v>50.01</v>
       </c>
       <c r="K5">
-        <v>68.666</v>
+        <v>373.7389999999995</v>
       </c>
       <c r="L5">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M5">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="N5">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="O5">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -693,43 +693,43 @@
         <v>20000</v>
       </c>
       <c r="D6">
-        <v>9232.317999999999</v>
+        <v>9226.184999999998</v>
       </c>
       <c r="E6">
-        <v>46.155</v>
+        <v>46.135</v>
       </c>
       <c r="F6">
-        <v>10767.682</v>
+        <v>10773.815</v>
       </c>
       <c r="G6">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H6">
-        <v>3024.473</v>
+        <v>3876.456999999999</v>
       </c>
       <c r="I6">
-        <v>3997.433</v>
+        <v>2414.293</v>
       </c>
       <c r="J6">
-        <v>849.6130000000001</v>
+        <v>1265.943</v>
       </c>
       <c r="K6">
-        <v>1360.799</v>
+        <v>1669.491999999999</v>
       </c>
       <c r="L6">
-        <v>25.815</v>
+        <v>26.8925</v>
       </c>
       <c r="M6">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="N6">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="O6">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="P6">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
